--- a/CDAC_PG_DITISS_Study_Checklist.xlsx
+++ b/CDAC_PG_DITISS_Study_Checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\veena\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SunBeam_Ditiss\DITISS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CDECA7-541C-4172-A3D2-0509DCF9B387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF9A947-DBF6-4918-8576-9BE8A0B9FC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="546" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="546" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Module Overview" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="705">
   <si>
     <t>Sr No</t>
   </si>
@@ -2149,6 +2149,12 @@
   </si>
   <si>
     <t>⏳ In Progress</t>
+  </si>
+  <si>
+    <t>CMD</t>
+  </si>
+  <si>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
@@ -2251,7 +2257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2377,13 +2383,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2435,6 +2454,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
@@ -3093,11 +3113,12 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{740DA186-DF4D-40D1-8E9A-2A23F2EDA10E}" name="Table5" displayName="Table5" ref="A1:B123" totalsRowShown="0" headerRowDxfId="56" headerRowBorderDxfId="55" tableBorderDxfId="54" headerRowCellStyle="Heading 1">
-  <autoFilter ref="A1:B123" xr:uid="{740DA186-DF4D-40D1-8E9A-2A23F2EDA10E}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{740DA186-DF4D-40D1-8E9A-2A23F2EDA10E}" name="Table5" displayName="Table5" ref="A1:C123" totalsRowShown="0" headerRowDxfId="56" headerRowBorderDxfId="55" tableBorderDxfId="54" headerRowCellStyle="Heading 1">
+  <autoFilter ref="A1:C123" xr:uid="{740DA186-DF4D-40D1-8E9A-2A23F2EDA10E}"/>
+  <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{6CEB8E28-CB4A-420F-87FA-236775BEBFBB}" name="Topic" dataDxfId="53"/>
     <tableColumn id="2" xr3:uid="{CABAC821-C4C6-44DD-9DE2-57CACF04FFAF}" name="Completed" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{D7131826-DD89-4A0F-BEC0-BF77298FE99E}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5977,7 +5998,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD093ADF-382F-41B1-AB6D-1F9283D5A037}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:B123"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="133.08984375" bestFit="1" customWidth="1"/>
@@ -5986,21 +6007,24 @@
     <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="20" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="22" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="17.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="C1" s="31" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>343</v>
       </c>
       <c r="B2" s="20"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>224</v>
       </c>
@@ -6008,7 +6032,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>225</v>
       </c>
@@ -6016,7 +6040,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>226</v>
       </c>
@@ -6024,7 +6048,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>227</v>
       </c>
@@ -6032,7 +6056,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>228</v>
       </c>
@@ -6040,7 +6064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>229</v>
       </c>
@@ -6048,7 +6072,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>230</v>
       </c>
@@ -6056,7 +6080,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>231</v>
       </c>
@@ -6064,7 +6088,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>232</v>
       </c>
@@ -6072,7 +6096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>233</v>
       </c>
@@ -6080,7 +6104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>234</v>
       </c>
@@ -6088,7 +6112,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>235</v>
       </c>
@@ -6096,7 +6120,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>236</v>
       </c>
@@ -6104,7 +6128,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>237</v>
       </c>
@@ -6746,7 +6770,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="6" t="s">
         <v>316</v>
       </c>
@@ -6754,7 +6778,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="6" t="s">
         <v>317</v>
       </c>
@@ -6762,7 +6786,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="6" t="s">
         <v>318</v>
       </c>
@@ -6770,7 +6794,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="6" t="s">
         <v>319</v>
       </c>
@@ -6778,7 +6802,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="6" t="s">
         <v>320</v>
       </c>
@@ -6786,7 +6810,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="6" t="s">
         <v>321</v>
       </c>
@@ -6794,7 +6818,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="6" t="s">
         <v>322</v>
       </c>
@@ -6802,7 +6826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="6" t="s">
         <v>323</v>
       </c>
@@ -6810,7 +6834,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="6" t="s">
         <v>324</v>
       </c>
@@ -6818,7 +6842,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="6" t="s">
         <v>325</v>
       </c>
@@ -6826,7 +6850,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="6" t="s">
         <v>326</v>
       </c>
@@ -6834,7 +6858,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="6" t="s">
         <v>327</v>
       </c>
@@ -6842,7 +6866,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="6" t="s">
         <v>328</v>
       </c>
@@ -6850,7 +6874,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
         <v>329</v>
       </c>
@@ -6858,7 +6882,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="6" t="s">
         <v>330</v>
       </c>
@@ -6866,12 +6890,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="6" t="s">
         <v>331</v>
       </c>
       <c r="B112" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
+      </c>
+      <c r="C112" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -6887,7 +6914,7 @@
         <v>333</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -6895,7 +6922,7 @@
         <v>334</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -6903,7 +6930,7 @@
         <v>335</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -6911,7 +6938,7 @@
         <v>336</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -6919,7 +6946,7 @@
         <v>337</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -6927,7 +6954,7 @@
         <v>338</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -6935,7 +6962,7 @@
         <v>339</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -6943,7 +6970,7 @@
         <v>340</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -6951,7 +6978,7 @@
         <v>341</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -6959,7 +6986,7 @@
         <v>342</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>23</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>
